--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="69">
   <si>
     <t>Result</t>
   </si>
@@ -428,6 +428,36 @@
   </si>
   <si>
     <t>Mon Nov 17 17:06:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:31:42 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:33:34 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:35:26 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:36:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:38:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:49:43 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:52:18 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:53:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:55:24 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:56:47 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -868,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1013,7 +1043,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -1158,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1301,7 +1331,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1446,7 +1476,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1589,7 +1619,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1734,7 +1764,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1877,7 +1907,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2022,7 +2052,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2165,7 +2195,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="70">
   <si>
     <t>Result</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>Fri Dec 26 20:56:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 17:08:12 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="81">
   <si>
     <t>Result</t>
   </si>
@@ -461,6 +461,39 @@
   </si>
   <si>
     <t>Fri Jan 09 17:08:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:45:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:46:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:48:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:50:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:51:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:01:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:02:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:05:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:07:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 22:46:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -901,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1046,7 +1079,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -1191,7 +1224,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1334,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1479,7 +1512,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1622,7 +1655,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1767,7 +1800,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1910,7 +1943,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2055,7 +2088,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2198,7 +2231,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="91">
   <si>
     <t>Result</t>
   </si>
@@ -494,6 +494,36 @@
   </si>
   <si>
     <t>Tue Mar 10 22:46:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:18:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:20:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:22:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:24:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:25:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:37:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:38:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:40:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:41:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:44:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -934,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1079,7 +1109,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -1224,7 +1254,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1367,7 +1397,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1512,7 +1542,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1655,7 +1685,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1800,7 +1830,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1943,7 +1973,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2088,7 +2118,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2231,7 +2261,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="94">
   <si>
     <t>Result</t>
   </si>
@@ -524,6 +524,15 @@
   </si>
   <si>
     <t>Tue Jun 02 11:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 18:57:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:13:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:38:28 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +1982,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2118,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="117">
   <si>
     <t>Result</t>
   </si>
@@ -533,6 +533,75 @@
   </si>
   <si>
     <t>Fri Jun 05 21:38:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:02:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:04:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:06:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:11:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:21:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:24:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:25:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:27:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:29:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 11:22:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 11:25:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:16:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:17:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:19:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:35:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:41:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:43:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:45:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:46:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:59:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:03:15 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -973,7 +1042,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1118,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -1263,7 +1332,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1406,7 +1475,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1551,7 +1620,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1694,7 +1763,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1839,7 +1908,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1982,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2127,7 +2196,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2270,7 +2339,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="127">
   <si>
     <t>Result</t>
   </si>
@@ -602,6 +602,36 @@
   </si>
   <si>
     <t>Fri Jun 19 13:03:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:48:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:51:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:00:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:03:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:04:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:05:57 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -984,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -1009,13 +1039,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1038,11 +1068,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>105</v>
+      <c r="B2" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1054,17 +1084,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1129,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A5AD8E-8FB3-4E0D-8FB3-58E3B5B29B16}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -1154,13 +1184,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1183,13 +1213,13 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1201,17 +1231,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1271,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2865416F-EAD8-4226-BA0B-0AD26ABF0604}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.81640625" collapsed="true"/>
@@ -1299,13 +1329,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1328,11 +1358,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>110</v>
+      <c r="B2" t="s" s="0">
+        <v>122</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1344,17 +1374,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1414,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3A7C80-3096-4B80-A8BF-99672E759DAB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.36328125" collapsed="true"/>
@@ -1442,13 +1472,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1471,11 +1501,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>104</v>
+      <c r="B2" t="s" s="0">
+        <v>117</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1487,17 +1517,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1559,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A397DB6E-BC66-4CE5-A0EA-21E31C3C1269}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.6328125" collapsed="true"/>
@@ -1587,13 +1617,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1616,11 +1646,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>112</v>
+      <c r="B2" t="s" s="0">
+        <v>124</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1632,17 +1662,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1702,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF2A858-8568-405F-B1FE-A4DB3A2B6FAB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
@@ -1730,13 +1760,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1759,11 +1789,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>106</v>
+      <c r="B2" t="s" s="0">
+        <v>119</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1775,17 +1805,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1847,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F06328A-9DEA-4031-BF6E-3E1679D9E636}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.26953125" collapsed="true"/>
@@ -1875,13 +1905,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1904,11 +1934,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>114</v>
+      <c r="B2" t="s" s="0">
+        <v>126</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1920,17 +1950,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1990,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900F5C47-9A3E-42DC-8852-58A42D0C9EFE}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="26.6328125" collapsed="true"/>
@@ -2018,13 +2048,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2047,11 +2077,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>108</v>
+      <c r="B2" t="s" s="0">
+        <v>121</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2063,17 +2093,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2135,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10510DE0-0B5B-490D-A8EE-5AFB1CF2AE1D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.1796875" collapsed="true"/>
@@ -2163,13 +2193,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2192,11 +2222,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>116</v>
+      <c r="B2" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2208,17 +2238,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2278,7 +2308,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EEE3BC-AF45-4450-AB4B-7E9300EF985A}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.26953125" collapsed="true"/>
@@ -2306,13 +2336,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2335,11 +2365,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>107</v>
+      <c r="B2" t="s" s="0">
+        <v>120</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2351,17 +2381,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="137">
   <si>
     <t>Result</t>
   </si>
@@ -632,6 +632,36 @@
   </si>
   <si>
     <t>Sat Aug 08 20:05:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:56:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:57:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:59:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:01:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:10:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:15:24 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1102,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1217,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>24</v>
@@ -1362,7 +1392,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1505,7 +1535,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1650,7 +1680,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1793,7 +1823,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1938,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2081,7 +2111,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2226,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2369,7 +2399,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
